--- a/artfynd/A 48370-2024 artfynd.xlsx
+++ b/artfynd/A 48370-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>67347412</v>
+        <v>67347405</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>546249.5561187776</v>
+        <v>546336</v>
       </c>
       <c r="R2" t="n">
-        <v>7043058.705546767</v>
+        <v>7043218</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2017-08-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67347414</v>
+        <v>67347411</v>
       </c>
       <c r="B3" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4660</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>546391.8012099443</v>
+        <v>546252</v>
       </c>
       <c r="R3" t="n">
-        <v>7042930.845612361</v>
+        <v>7043062</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2017-08-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-08-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67347413</v>
+        <v>67347407</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>546394.036223697</v>
+        <v>546238</v>
       </c>
       <c r="R4" t="n">
-        <v>7042930.878164398</v>
+        <v>7043174</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2017-08-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-08-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67347415</v>
+        <v>67347414</v>
       </c>
       <c r="B5" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>4660</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>546333.0975841259</v>
+        <v>546392</v>
       </c>
       <c r="R5" t="n">
-        <v>7042847.834344828</v>
+        <v>7042931</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2017-08-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-08-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67347411</v>
+        <v>67347406</v>
       </c>
       <c r="B6" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1205</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546252.1926529208</v>
+        <v>546243</v>
       </c>
       <c r="R6" t="n">
-        <v>7043061.869192689</v>
+        <v>7043184</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2017-08-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-08-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,6 +1173,511 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>67347410</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ögonfägnadens vindkraftpark, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>546131</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7043068</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>67347417</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ögonfägnadens vindkraftpark, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>546471</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7042835</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>67347415</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ögonfägnadens vindkraftpark, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>546333</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7042848</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>67347412</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ögonfägnadens vindkraftpark, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>546250</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7043059</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>67347413</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ögonfägnadens vindkraftpark, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>546394</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7042931</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2017-08-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 48370-2024 artfynd.xlsx
+++ b/artfynd/A 48370-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67347405</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67347411</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67347407</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67347414</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67347406</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67347410</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67347417</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67347415</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67347412</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,8 +1732,25 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67347413</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>